--- a/data/trans_dic/P19C04-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C04-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,86; 26,95</t>
+          <t>14,85; 26,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,37; 36,22</t>
+          <t>24,32; 36,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,68; 25,83</t>
+          <t>15,64; 26,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,47; 17,8</t>
+          <t>9,91; 17,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,99; 20,64</t>
+          <t>10,77; 20,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,6; 25,7</t>
+          <t>14,42; 25,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,77; 19,29</t>
+          <t>10,21; 19,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 13,62</t>
+          <t>8,19; 13,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,0; 21,69</t>
+          <t>14,43; 22,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,71; 28,59</t>
+          <t>21,2; 29,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,96; 21,06</t>
+          <t>14,12; 21,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,69; 14,64</t>
+          <t>9,76; 14,6</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,1; 27,87</t>
+          <t>19,94; 28,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,46; 33,28</t>
+          <t>23,49; 32,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,56; 22,74</t>
+          <t>14,47; 22,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,36; 11,66</t>
+          <t>5,2; 12,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,91; 23,88</t>
+          <t>16,17; 23,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,96; 21,6</t>
+          <t>14,51; 21,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,36; 16,09</t>
+          <t>9,69; 16,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,22; 10,27</t>
+          <t>6,43; 10,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,76; 24,37</t>
+          <t>18,97; 24,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,71; 25,87</t>
+          <t>19,82; 26,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 18,35</t>
+          <t>13,12; 18,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,93</t>
+          <t>6,34; 10,07</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,32; 27,0</t>
+          <t>16,18; 26,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,59; 33,34</t>
+          <t>23,07; 33,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 14,68</t>
+          <t>8,0; 15,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,53; 22,9</t>
+          <t>14,29; 22,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,98; 16,39</t>
+          <t>9,12; 17,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,61; 24,56</t>
+          <t>16,57; 25,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 11,93</t>
+          <t>5,95; 12,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,82; 19,07</t>
+          <t>12,47; 19,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,41; 19,89</t>
+          <t>13,42; 20,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,44; 27,35</t>
+          <t>20,36; 27,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,43; 12,14</t>
+          <t>7,38; 12,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,67; 19,36</t>
+          <t>14,6; 19,61</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,09; 21,44</t>
+          <t>11,93; 20,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,63; 34,05</t>
+          <t>23,24; 33,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,62; 27,93</t>
+          <t>18,4; 27,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,3; 21,58</t>
+          <t>11,59; 21,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,42; 15,86</t>
+          <t>8,34; 15,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,36; 22,52</t>
+          <t>14,63; 22,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,74; 17,6</t>
+          <t>9,92; 17,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,77; 10,86</t>
+          <t>5,21; 11,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,02; 16,37</t>
+          <t>11,08; 16,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,8; 26,94</t>
+          <t>19,87; 26,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,73; 20,91</t>
+          <t>15,24; 21,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 14,32</t>
+          <t>8,21; 14,21</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,7; 28,41</t>
+          <t>16,11; 28,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,07; 35,61</t>
+          <t>22,13; 36,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,52; 24,29</t>
+          <t>10,7; 24,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,73; 26,64</t>
+          <t>16,51; 26,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,03; 22,65</t>
+          <t>9,37; 21,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,49; 28,84</t>
+          <t>16,39; 28,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,23; 23,25</t>
+          <t>10,21; 23,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,64; 16,4</t>
+          <t>10,2; 16,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,15; 22,21</t>
+          <t>14,0; 22,73</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,42; 29,71</t>
+          <t>21,25; 30,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,57; 21,32</t>
+          <t>12,09; 21,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,12; 19,6</t>
+          <t>13,86; 19,49</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,51; 21,78</t>
+          <t>10,8; 21,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,21; 38,62</t>
+          <t>26,49; 38,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,38; 35,02</t>
+          <t>22,04; 34,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,85; 24,07</t>
+          <t>16,2; 24,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,48; 14,82</t>
+          <t>6,27; 14,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,35; 29,56</t>
+          <t>18,25; 28,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,71; 25,89</t>
+          <t>15,26; 25,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,5; 23,6</t>
+          <t>16,63; 23,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,75; 16,61</t>
+          <t>9,82; 16,58</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23,96; 32,26</t>
+          <t>24,13; 32,07</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20,08; 27,95</t>
+          <t>20,22; 28,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,19; 22,71</t>
+          <t>17,26; 22,48</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,2; 23,48</t>
+          <t>15,89; 23,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,82; 23,74</t>
+          <t>16,68; 23,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,29; 17,34</t>
+          <t>10,29; 17,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,21; 15,79</t>
+          <t>9,6; 15,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,46; 18,85</t>
+          <t>12,04; 18,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,5; 16,25</t>
+          <t>10,44; 16,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,84; 13,5</t>
+          <t>7,63; 13,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,26; 10,25</t>
+          <t>3,06; 9,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,97; 19,77</t>
+          <t>14,83; 19,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,47; 18,84</t>
+          <t>14,57; 19,04</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,84; 14,36</t>
+          <t>9,82; 14,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,61; 11,48</t>
+          <t>5,77; 11,54</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,58; 23,67</t>
+          <t>16,69; 23,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,85; 20,12</t>
+          <t>13,97; 20,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,66; 19,51</t>
+          <t>13,81; 19,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,48; 22,34</t>
+          <t>6,53; 22,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,55; 17,48</t>
+          <t>11,77; 17,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,76; 18,22</t>
+          <t>12,83; 18,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,88; 16,21</t>
+          <t>11,09; 16,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,56; 13,59</t>
+          <t>9,61; 13,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,88; 19,26</t>
+          <t>14,78; 19,53</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13,99; 18,17</t>
+          <t>13,98; 18,04</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12,9; 16,88</t>
+          <t>12,82; 16,86</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,34; 16,73</t>
+          <t>8,43; 16,83</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,37; 21,65</t>
+          <t>18,3; 21,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23,07; 26,49</t>
+          <t>23,2; 26,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16,39; 19,45</t>
+          <t>16,41; 19,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,18; 16,24</t>
+          <t>11,22; 16,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,28; 15,96</t>
+          <t>13,46; 16,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,21; 18,88</t>
+          <t>16,13; 18,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,7; 14,42</t>
+          <t>11,64; 14,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,63; 11,67</t>
+          <t>8,53; 11,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,06; 18,26</t>
+          <t>16,14; 18,21</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,98; 22,12</t>
+          <t>19,87; 22,09</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14,36; 16,34</t>
+          <t>14,4; 16,39</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,75; 13,57</t>
+          <t>10,93; 13,63</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28453; 51610</t>
+          <t>28440; 51546</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>61049; 90755</t>
+          <t>60933; 90379</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35990; 63334</t>
+          <t>38353; 64667</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28926; 54375</t>
+          <t>30276; 54638</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20099; 41524</t>
+          <t>21679; 41671</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36390; 64065</t>
+          <t>35933; 64386</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23956; 47316</t>
+          <t>25039; 46855</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23301; 39166</t>
+          <t>23566; 39763</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54992; 85200</t>
+          <t>56687; 87452</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>103502; 142886</t>
+          <t>105949; 148281</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68469; 103270</t>
+          <t>69235; 103151</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57452; 86827</t>
+          <t>57861; 86588</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78252; 114191</t>
+          <t>81692; 115983</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95323; 135206</t>
+          <t>95454; 132596</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52863; 82596</t>
+          <t>52535; 81545</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27178; 59129</t>
+          <t>26340; 61556</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70191; 105360</t>
+          <t>71332; 105180</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61128; 94584</t>
+          <t>63507; 95878</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36823; 63282</t>
+          <t>38120; 65739</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31197; 51516</t>
+          <t>32255; 52996</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>159621; 207383</t>
+          <t>161421; 207568</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>166396; 218423</t>
+          <t>167342; 220540</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97844; 138812</t>
+          <t>99274; 140851</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>62312; 100164</t>
+          <t>63944; 101574</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>38613; 63857</t>
+          <t>38283; 62508</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>66348; 97899</t>
+          <t>67750; 97587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22492; 42650</t>
+          <t>23251; 45005</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43752; 68963</t>
+          <t>43053; 66572</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25935; 47325</t>
+          <t>26351; 49411</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51332; 80744</t>
+          <t>54478; 82877</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17447; 36731</t>
+          <t>18306; 37114</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>42997; 63932</t>
+          <t>41825; 63925</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>70436; 104511</t>
+          <t>70519; 107061</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>127246; 170234</t>
+          <t>126701; 168058</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44475; 72620</t>
+          <t>44172; 72500</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>93391; 123239</t>
+          <t>92929; 124806</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32346; 57345</t>
+          <t>31906; 55988</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73969; 106601</t>
+          <t>72769; 105113</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61466; 92196</t>
+          <t>60730; 91018</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35029; 66921</t>
+          <t>35953; 65807</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25221; 47511</t>
+          <t>24982; 47198</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49231; 77206</t>
+          <t>50139; 78130</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33994; 61415</t>
+          <t>34593; 61168</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22592; 51395</t>
+          <t>24665; 52521</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62480; 92818</t>
+          <t>62811; 94678</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>129884; 176694</t>
+          <t>130324; 173382</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>100031; 141954</t>
+          <t>103436; 143442</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>61563; 112202</t>
+          <t>64331; 111353</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26727; 48382</t>
+          <t>27430; 48286</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>42389; 68400</t>
+          <t>42504; 69149</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12537; 28954</t>
+          <t>12753; 28854</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28174; 44877</t>
+          <t>27812; 44163</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17448; 39391</t>
+          <t>16302; 36830</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32253; 56406</t>
+          <t>32046; 54915</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14886; 33828</t>
+          <t>14855; 33653</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21532; 33167</t>
+          <t>20632; 33091</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>48689; 76455</t>
+          <t>48181; 78233</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83014; 115175</t>
+          <t>82389; 116592</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33280; 56435</t>
+          <t>32010; 55609</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>52358; 72654</t>
+          <t>51383; 72271</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19891; 41222</t>
+          <t>20434; 40476</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>65514; 96540</t>
+          <t>66207; 97039</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>54615; 81819</t>
+          <t>51498; 80296</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40206; 61063</t>
+          <t>41094; 61183</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13244; 30307</t>
+          <t>12824; 30182</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48608; 78292</t>
+          <t>48321; 75518</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38825; 63990</t>
+          <t>37720; 63344</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>40659; 58138</t>
+          <t>40974; 58073</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38377; 65384</t>
+          <t>38661; 65304</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>123338; 166084</t>
+          <t>124211; 165103</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96524; 134366</t>
+          <t>97205; 137327</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>85980; 113565</t>
+          <t>86292; 112413</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>75201; 109008</t>
+          <t>73776; 108996</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>96712; 136542</t>
+          <t>95900; 137512</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>45510; 76711</t>
+          <t>45526; 76358</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55231; 94701</t>
+          <t>57575; 93712</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>67222; 101666</t>
+          <t>64939; 99203</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>65613; 101571</t>
+          <t>65266; 102623</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38167; 65751</t>
+          <t>37183; 66552</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>27045; 84900</t>
+          <t>25345; 82025</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>150217; 198383</t>
+          <t>148818; 197939</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>173701; 226106</t>
+          <t>174886; 228519</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91457; 133437</t>
+          <t>91281; 132408</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>80179; 163943</t>
+          <t>82405; 164790</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>87156; 124422</t>
+          <t>87729; 122785</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>87775; 127571</t>
+          <t>88560; 127723</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>87481; 124890</t>
+          <t>88420; 123886</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>58852; 202711</t>
+          <t>59281; 201075</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>68405; 103541</t>
+          <t>69700; 104861</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>89500; 127787</t>
+          <t>89977; 129086</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>75210; 112067</t>
+          <t>76651; 112808</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>67275; 95637</t>
+          <t>67629; 94783</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>166405; 215281</t>
+          <t>165256; 218355</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>186784; 242594</t>
+          <t>186647; 240891</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>171718; 224725</t>
+          <t>170670; 224448</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>118247; 269668</t>
+          <t>135846; 271269</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>450878; 531386</t>
+          <t>449175; 530224</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>672392; 772075</t>
+          <t>676315; 774731</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>436630; 518235</t>
+          <t>437264; 516550</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>374856; 544619</t>
+          <t>376258; 540180</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>364094; 437561</t>
+          <t>368865; 439813</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>509695; 593783</t>
+          <t>507321; 592332</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>335473; 413296</t>
+          <t>333507; 410704</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>308764; 417583</t>
+          <t>305337; 415367</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>834415; 948895</t>
+          <t>838333; 946159</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1210693; 1340636</t>
+          <t>1204086; 1338789</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>794359; 903583</t>
+          <t>796671; 906223</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>745530; 940970</t>
+          <t>757706; 944760</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C04-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C04-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,85; 26,92</t>
+          <t>14,99; 26,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,32; 36,07</t>
+          <t>23,98; 36,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,64; 26,37</t>
+          <t>15,62; 26,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,91; 17,89</t>
+          <t>11,68; 19,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,77; 20,71</t>
+          <t>10,79; 20,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,42; 25,83</t>
+          <t>14,86; 25,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,21; 19,11</t>
+          <t>9,75; 18,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,19; 13,83</t>
+          <t>8,08; 13,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,43; 22,27</t>
+          <t>14,39; 21,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,2; 29,67</t>
+          <t>21,55; 29,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,12; 21,03</t>
+          <t>14,23; 21,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,76; 14,6</t>
+          <t>10,64; 15,59</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,94; 28,31</t>
+          <t>19,95; 28,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,49; 32,63</t>
+          <t>23,77; 32,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,47; 22,45</t>
+          <t>14,17; 22,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 12,14</t>
+          <t>5,06; 11,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,17; 23,84</t>
+          <t>16,09; 23,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,51; 21,9</t>
+          <t>14,59; 21,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,69; 16,71</t>
+          <t>9,57; 16,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,57</t>
+          <t>6,15; 10,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,97; 24,39</t>
+          <t>18,83; 24,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,82; 26,13</t>
+          <t>19,97; 25,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,12; 18,62</t>
+          <t>13,11; 18,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,07</t>
+          <t>6,26; 9,64</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,18; 26,43</t>
+          <t>16,44; 27,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,07; 33,23</t>
+          <t>22,76; 33,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,0; 15,49</t>
+          <t>7,94; 14,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,29; 22,1</t>
+          <t>15,73; 23,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,12; 17,11</t>
+          <t>8,93; 16,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,57; 25,21</t>
+          <t>15,65; 24,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 12,06</t>
+          <t>5,47; 11,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,47; 19,07</t>
+          <t>13,24; 19,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,42; 20,38</t>
+          <t>13,34; 19,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,36; 27,0</t>
+          <t>20,27; 27,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 12,12</t>
+          <t>7,5; 12,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,6; 19,61</t>
+          <t>15,24; 20,35</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,93; 20,93</t>
+          <t>11,93; 20,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,24; 33,57</t>
+          <t>23,76; 34,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,4; 27,58</t>
+          <t>19,16; 28,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,59; 21,22</t>
+          <t>12,54; 22,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,34; 15,76</t>
+          <t>8,35; 15,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,63; 22,79</t>
+          <t>13,93; 22,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,92; 17,53</t>
+          <t>10,11; 17,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,21; 11,09</t>
+          <t>7,99; 13,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,08; 16,7</t>
+          <t>11,15; 16,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,87; 26,43</t>
+          <t>19,98; 26,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,24; 21,13</t>
+          <t>14,9; 21,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 14,21</t>
+          <t>11,16; 16,51</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,11; 28,36</t>
+          <t>16,05; 27,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,13; 36,0</t>
+          <t>22,11; 35,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,7; 24,2</t>
+          <t>10,72; 23,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,51; 26,22</t>
+          <t>17,55; 27,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,37; 21,18</t>
+          <t>9,88; 21,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,39; 28,08</t>
+          <t>16,64; 28,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,21; 23,13</t>
+          <t>10,22; 22,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,2; 16,36</t>
+          <t>10,89; 17,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,0; 22,73</t>
+          <t>14,31; 22,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,25; 30,08</t>
+          <t>20,92; 30,47</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,09; 21,01</t>
+          <t>12,14; 21,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,86; 19,49</t>
+          <t>15,05; 20,65</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,8; 21,39</t>
+          <t>10,9; 21,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,49; 38,82</t>
+          <t>26,64; 39,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,04; 34,37</t>
+          <t>22,89; 34,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,2; 24,11</t>
+          <t>16,41; 24,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,27; 14,76</t>
+          <t>6,77; 14,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,25; 28,52</t>
+          <t>18,25; 28,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,26; 25,63</t>
+          <t>15,64; 26,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,63; 23,57</t>
+          <t>16,92; 24,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,82; 16,58</t>
+          <t>9,91; 16,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,13; 32,07</t>
+          <t>23,89; 31,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20,22; 28,56</t>
+          <t>20,36; 28,5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,26; 22,48</t>
+          <t>17,57; 22,98</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,89; 23,47</t>
+          <t>16,07; 23,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,68; 23,91</t>
+          <t>17,06; 24,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,29; 17,26</t>
+          <t>10,4; 17,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,6; 15,63</t>
+          <t>9,61; 15,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,04; 18,39</t>
+          <t>12,46; 18,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,44; 16,42</t>
+          <t>10,54; 16,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,63; 13,66</t>
+          <t>7,77; 13,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 9,9</t>
+          <t>7,5; 11,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,83; 19,72</t>
+          <t>14,73; 19,42</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,57; 19,04</t>
+          <t>14,52; 18,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,82; 14,25</t>
+          <t>9,9; 14,18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,77; 11,54</t>
+          <t>9,21; 12,5</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,69; 23,36</t>
+          <t>16,49; 23,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,97; 20,15</t>
+          <t>13,98; 20,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,81; 19,35</t>
+          <t>13,32; 19,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,53; 22,16</t>
+          <t>18,71; 24,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,77; 17,7</t>
+          <t>11,4; 17,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,83; 18,41</t>
+          <t>12,9; 18,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,09; 16,32</t>
+          <t>10,82; 16,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,61; 13,46</t>
+          <t>9,91; 13,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,78; 19,53</t>
+          <t>14,96; 19,14</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13,98; 18,04</t>
+          <t>14,09; 18,37</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12,82; 16,86</t>
+          <t>12,96; 16,84</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,43; 16,83</t>
+          <t>14,95; 18,58</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,3; 21,6</t>
+          <t>18,43; 21,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23,2; 26,58</t>
+          <t>22,96; 26,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16,41; 19,39</t>
+          <t>16,5; 19,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,22; 16,11</t>
+          <t>14,83; 17,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,46; 16,05</t>
+          <t>13,43; 16,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,13; 18,83</t>
+          <t>16,28; 19,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,64; 14,33</t>
+          <t>11,77; 14,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,53; 11,61</t>
+          <t>10,7; 12,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,14; 18,21</t>
+          <t>16,14; 18,29</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,87; 22,09</t>
+          <t>19,9; 22,08</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14,4; 16,39</t>
+          <t>14,29; 16,27</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,93; 13,63</t>
+          <t>13,05; 14,63</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40785</t>
+          <t>46232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30118</t>
+          <t>32322</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70903</t>
+          <t>78554</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28440; 51546</t>
+          <t>28705; 51260</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>60933; 90379</t>
+          <t>60088; 90444</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38353; 64667</t>
+          <t>38308; 65321</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30276; 54638</t>
+          <t>35161; 58331</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21679; 41671</t>
+          <t>21717; 41809</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35933; 64386</t>
+          <t>37036; 63751</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25039; 46855</t>
+          <t>23915; 46280</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23566; 39763</t>
+          <t>24997; 42074</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>56687; 87452</t>
+          <t>56508; 85643</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>105949; 148281</t>
+          <t>107689; 145540</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>69235; 103151</t>
+          <t>69783; 103230</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57861; 86588</t>
+          <t>64954; 95140</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38899</t>
+          <t>39385</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>40993</t>
+          <t>42079</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79892</t>
+          <t>81463</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81692; 115983</t>
+          <t>81736; 116551</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95454; 132596</t>
+          <t>96565; 133304</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52535; 81545</t>
+          <t>51454; 81345</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26340; 61556</t>
+          <t>26229; 57243</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71332; 105180</t>
+          <t>70970; 102794</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63507; 95878</t>
+          <t>63857; 94087</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38120; 65739</t>
+          <t>37661; 64656</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32255; 52996</t>
+          <t>32697; 53454</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>161421; 207568</t>
+          <t>160210; 210200</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>167342; 220540</t>
+          <t>168607; 217534</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>99274; 140851</t>
+          <t>99169; 138299</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>63944; 101574</t>
+          <t>65682; 101180</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54870</t>
+          <t>58455</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52908</t>
+          <t>54857</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>107778</t>
+          <t>113312</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>38283; 62508</t>
+          <t>38876; 64881</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>67750; 97587</t>
+          <t>66848; 98031</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23251; 45005</t>
+          <t>23061; 43194</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43053; 66572</t>
+          <t>47224; 71966</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26351; 49411</t>
+          <t>25780; 47321</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54478; 82877</t>
+          <t>51458; 81528</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18306; 37114</t>
+          <t>16848; 35937</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41825; 63925</t>
+          <t>45225; 66982</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>70519; 107061</t>
+          <t>70057; 102691</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>126701; 168058</t>
+          <t>126185; 169026</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44172; 72500</t>
+          <t>44869; 72490</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>92929; 124806</t>
+          <t>97814; 130625</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49848</t>
+          <t>63492</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>37739</t>
+          <t>43408</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87587</t>
+          <t>106900</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31906; 55988</t>
+          <t>31919; 53826</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>72769; 105113</t>
+          <t>74395; 107066</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60730; 91018</t>
+          <t>63225; 94472</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35953; 65807</t>
+          <t>46477; 83558</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24982; 47198</t>
+          <t>25011; 46641</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50139; 78130</t>
+          <t>47771; 77509</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34593; 61168</t>
+          <t>35265; 61214</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24665; 52521</t>
+          <t>33529; 55370</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62811; 94678</t>
+          <t>63211; 93449</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>130324; 173382</t>
+          <t>131067; 176823</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103436; 143442</t>
+          <t>101162; 142830</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>64331; 111353</t>
+          <t>88177; 130526</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35463</t>
+          <t>42500</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26441</t>
+          <t>29975</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61904</t>
+          <t>72475</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>27430; 48286</t>
+          <t>27336; 47643</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>42504; 69149</t>
+          <t>42461; 68711</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12753; 28854</t>
+          <t>12786; 28304</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27812; 44163</t>
+          <t>33214; 52388</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16302; 36830</t>
+          <t>17175; 37831</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32046; 54915</t>
+          <t>32537; 55649</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14855; 33653</t>
+          <t>14871; 32755</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20632; 33091</t>
+          <t>23929; 38468</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>48181; 78233</t>
+          <t>49268; 78316</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>82389; 116592</t>
+          <t>81082; 118125</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32010; 55609</t>
+          <t>32142; 55869</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>51383; 72271</t>
+          <t>61552; 84490</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50285</t>
+          <t>50439</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>48900</t>
+          <t>50797</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99185</t>
+          <t>101236</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20434; 40476</t>
+          <t>20638; 40201</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>66207; 97039</t>
+          <t>66581; 98324</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51498; 80296</t>
+          <t>53477; 80371</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41094; 61183</t>
+          <t>40987; 61688</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12824; 30182</t>
+          <t>13853; 30506</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48321; 75518</t>
+          <t>48338; 76217</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37720; 63344</t>
+          <t>38646; 64276</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>40974; 58073</t>
+          <t>42564; 61213</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38661; 65304</t>
+          <t>39015; 65055</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>124211; 165103</t>
+          <t>122961; 164334</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>97205; 137327</t>
+          <t>97884; 137028</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>86292; 112413</t>
+          <t>88088; 115202</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>73411</t>
+          <t>86540</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>58863</t>
+          <t>68192</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>154732</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>73776; 108996</t>
+          <t>74636; 109355</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>95900; 137512</t>
+          <t>98117; 139025</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>45526; 76358</t>
+          <t>46011; 75916</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>57575; 93712</t>
+          <t>67075; 106651</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>64939; 99203</t>
+          <t>67227; 99491</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>65266; 102623</t>
+          <t>65887; 103852</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37183; 66552</t>
+          <t>37864; 65182</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>25345; 82025</t>
+          <t>55578; 82858</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>148818; 197939</t>
+          <t>147891; 194917</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>174886; 228519</t>
+          <t>174198; 227038</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91281; 132408</t>
+          <t>92042; 131752</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>82405; 164790</t>
+          <t>132551; 179911</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>141416</t>
+          <t>168874</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>80439</t>
+          <t>95486</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>221855</t>
+          <t>264360</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>87729; 122785</t>
+          <t>86650; 122924</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>88560; 127723</t>
+          <t>88625; 127783</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>88420; 123886</t>
+          <t>85307; 123792</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>59281; 201075</t>
+          <t>144052; 191548</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>69700; 104861</t>
+          <t>67521; 102794</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>89977; 129086</t>
+          <t>90493; 130476</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>76651; 112808</t>
+          <t>74774; 111553</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>67629; 94783</t>
+          <t>80299; 112561</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>165256; 218355</t>
+          <t>167240; 213980</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>186647; 240891</t>
+          <t>188088; 245221</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>170670; 224448</t>
+          <t>172530; 224252</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>135846; 271269</t>
+          <t>236188; 293632</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>484977</t>
+          <t>555917</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>376402</t>
+          <t>417116</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>861379</t>
+          <t>973032</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>449175; 530224</t>
+          <t>452315; 532460</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>676315; 774731</t>
+          <t>669120; 766749</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>437264; 516550</t>
+          <t>439636; 519767</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>376258; 540180</t>
+          <t>503648; 599034</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>368865; 439813</t>
+          <t>368079; 443924</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>507321; 592332</t>
+          <t>512065; 603803</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>333507; 410704</t>
+          <t>337268; 413031</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>305337; 415367</t>
+          <t>388067; 448988</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>838333; 946159</t>
+          <t>838459; 950149</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1204086; 1338789</t>
+          <t>1206019; 1337771</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>796671; 906223</t>
+          <t>790208; 899820</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>757706; 944760</t>
+          <t>916155; 1027041</t>
         </is>
       </c>
     </row>
